--- a/AtchisonRegime/Outputs/Canada/df_regCLI_Canada.xlsx
+++ b/AtchisonRegime/Outputs/Canada/df_regCLI_Canada.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H797"/>
+  <dimension ref="A1:H798"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20891,22 +20891,22 @@
         <v>45443</v>
       </c>
       <c r="B787" t="n">
-        <v>98.68000000000001</v>
+        <v>98.67377999999999</v>
       </c>
       <c r="C787" t="n">
-        <v>98.47666666666667</v>
+        <v>98.47459333333332</v>
       </c>
       <c r="D787" t="n">
-        <v>99.88944444444445</v>
+        <v>99.88927166666666</v>
       </c>
       <c r="E787" t="n">
-        <v>2.220250879574985</v>
+        <v>2.220347926349018</v>
       </c>
       <c r="F787" t="b">
         <v>1</v>
       </c>
       <c r="G787" t="n">
-        <v>0.09458390577924577</v>
+        <v>0.09177840895191415</v>
       </c>
       <c r="H787" t="b">
         <v>1</v>
@@ -20917,22 +20917,22 @@
         <v>45473</v>
       </c>
       <c r="B788" t="n">
-        <v>98.92</v>
+        <v>98.91126</v>
       </c>
       <c r="C788" t="n">
-        <v>98.69</v>
+        <v>98.68501333333332</v>
       </c>
       <c r="D788" t="n">
-        <v>99.76972222222223</v>
+        <v>99.76930666666667</v>
       </c>
       <c r="E788" t="n">
-        <v>2.150066425699486</v>
+        <v>2.150255900853156</v>
       </c>
       <c r="F788" t="b">
         <v>1</v>
       </c>
       <c r="G788" t="n">
-        <v>0.1116244582638488</v>
+        <v>0.1104426686636601</v>
       </c>
       <c r="H788" t="b">
         <v>1</v>
@@ -20943,22 +20943,22 @@
         <v>45504</v>
       </c>
       <c r="B789" t="n">
-        <v>99.19</v>
+        <v>99.17975</v>
       </c>
       <c r="C789" t="n">
-        <v>98.93000000000001</v>
+        <v>98.92159666666667</v>
       </c>
       <c r="D789" t="n">
-        <v>99.65444444444444</v>
+        <v>99.65374416666666</v>
       </c>
       <c r="E789" t="n">
-        <v>2.062649398148428</v>
+        <v>2.062889600690246</v>
       </c>
       <c r="F789" t="b">
         <v>1</v>
       </c>
       <c r="G789" t="n">
-        <v>0.1308996091349146</v>
+        <v>0.1301523842624262</v>
       </c>
       <c r="H789" t="b">
         <v>1</v>
@@ -20969,22 +20969,22 @@
         <v>45535</v>
       </c>
       <c r="B790" t="n">
-        <v>99.48999999999999</v>
+        <v>99.47515</v>
       </c>
       <c r="C790" t="n">
-        <v>99.2</v>
+        <v>99.18871999999999</v>
       </c>
       <c r="D790" t="n">
-        <v>99.54805555555555</v>
+        <v>99.54694277777779</v>
       </c>
       <c r="E790" t="n">
-        <v>1.964626928516837</v>
+        <v>1.964854057707275</v>
       </c>
       <c r="F790" t="b">
         <v>1</v>
       </c>
       <c r="G790" t="n">
-        <v>0.1527007472235339</v>
+        <v>0.1503419548343929</v>
       </c>
       <c r="H790" t="b">
         <v>1</v>
@@ -20995,22 +20995,22 @@
         <v>45565</v>
       </c>
       <c r="B791" t="n">
-        <v>99.81</v>
+        <v>99.78751</v>
       </c>
       <c r="C791" t="n">
-        <v>99.49666666666667</v>
+        <v>99.48080333333333</v>
       </c>
       <c r="D791" t="n">
-        <v>99.45194444444445</v>
+        <v>99.45020694444445</v>
       </c>
       <c r="E791" t="n">
-        <v>1.859145455685585</v>
+        <v>1.859205954312969</v>
       </c>
       <c r="F791" t="b">
         <v>1</v>
       </c>
       <c r="G791" t="n">
-        <v>0.1721220892219018</v>
+        <v>0.16800720720337</v>
       </c>
       <c r="H791" t="b">
         <v>1</v>
@@ -21021,22 +21021,22 @@
         <v>45596</v>
       </c>
       <c r="B792" t="n">
-        <v>100.12</v>
+        <v>100.0905</v>
       </c>
       <c r="C792" t="n">
-        <v>99.80666666666666</v>
+        <v>99.78438666666666</v>
       </c>
       <c r="D792" t="n">
-        <v>99.36611111111112</v>
+        <v>99.36355416666667</v>
       </c>
       <c r="E792" t="n">
-        <v>1.748737140710726</v>
+        <v>1.748356414754475</v>
       </c>
       <c r="F792" t="b">
         <v>1</v>
       </c>
       <c r="G792" t="n">
-        <v>0.1772707817448261</v>
+        <v>0.1732999046664966</v>
       </c>
       <c r="H792" t="b">
         <v>1</v>
@@ -21047,22 +21047,22 @@
         <v>45626</v>
       </c>
       <c r="B793" t="n">
-        <v>100.4</v>
+        <v>100.3501</v>
       </c>
       <c r="C793" t="n">
-        <v>100.11</v>
+        <v>100.0760366666667</v>
       </c>
       <c r="D793" t="n">
-        <v>99.29055555555556</v>
+        <v>99.2866125</v>
       </c>
       <c r="E793" t="n">
-        <v>1.637110598313581</v>
+        <v>1.635634625768581</v>
       </c>
       <c r="F793" t="b">
         <v>1</v>
       </c>
       <c r="G793" t="n">
-        <v>0.1710330385060329</v>
+        <v>0.1587151530727753</v>
       </c>
       <c r="H793" t="b">
         <v>1</v>
@@ -21073,22 +21073,22 @@
         <v>45657</v>
       </c>
       <c r="B794" t="n">
-        <v>100.63</v>
+        <v>100.5443</v>
       </c>
       <c r="C794" t="n">
-        <v>100.3833333333333</v>
+        <v>100.3283</v>
       </c>
       <c r="D794" t="n">
-        <v>99.22499999999999</v>
+        <v>99.21867638888889</v>
       </c>
       <c r="E794" t="n">
-        <v>1.528380094834153</v>
+        <v>1.524430287409649</v>
       </c>
       <c r="F794" t="b">
         <v>1</v>
       </c>
       <c r="G794" t="n">
-        <v>0.150486126309403</v>
+        <v>0.1273918536019111</v>
       </c>
       <c r="H794" t="b">
         <v>1</v>
@@ -21099,22 +21099,22 @@
         <v>45688</v>
       </c>
       <c r="B795" t="n">
-        <v>100.8</v>
+        <v>100.6711</v>
       </c>
       <c r="C795" t="n">
-        <v>100.61</v>
+        <v>100.5218333333333</v>
       </c>
       <c r="D795" t="n">
-        <v>99.16916666666667</v>
+        <v>99.15926250000001</v>
       </c>
       <c r="E795" t="n">
-        <v>1.42702763012578</v>
+        <v>1.418459106016705</v>
       </c>
       <c r="F795" t="b">
         <v>1</v>
       </c>
       <c r="G795" t="n">
-        <v>0.1191287375318849</v>
+        <v>0.08939277802379972</v>
       </c>
       <c r="H795" t="b">
         <v>1</v>
@@ -21125,22 +21125,22 @@
         <v>45716</v>
       </c>
       <c r="B796" t="n">
-        <v>100.9</v>
+        <v>100.7282</v>
       </c>
       <c r="C796" t="n">
-        <v>100.7766666666667</v>
+        <v>100.6478666666667</v>
       </c>
       <c r="D796" t="n">
-        <v>99.12222222222222</v>
+        <v>99.10754583333333</v>
       </c>
       <c r="E796" t="n">
-        <v>1.336184570465004</v>
+        <v>1.320348841734745</v>
       </c>
       <c r="F796" t="b">
         <v>1</v>
       </c>
       <c r="G796" t="n">
-        <v>0.07483996014503268</v>
+        <v>0.04324614692355425</v>
       </c>
       <c r="H796" t="b">
         <v>1</v>
@@ -21151,24 +21151,50 @@
         <v>45747</v>
       </c>
       <c r="B797" t="n">
-        <v>100.97</v>
+        <v>100.7495</v>
       </c>
       <c r="C797" t="n">
-        <v>100.89</v>
+        <v>100.7162666666667</v>
       </c>
       <c r="D797" t="n">
-        <v>99.08527777777778</v>
+        <v>99.06447638888889</v>
       </c>
       <c r="E797" t="n">
-        <v>1.262146665942096</v>
+        <v>1.235819079928259</v>
       </c>
       <c r="F797" t="b">
         <v>1</v>
       </c>
       <c r="G797" t="n">
-        <v>0.05546106636326892</v>
+        <v>0.01723553256778737</v>
       </c>
       <c r="H797" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B798" t="n">
+        <v>100.7698</v>
+      </c>
+      <c r="C798" t="n">
+        <v>100.7491666666667</v>
+      </c>
+      <c r="D798" t="n">
+        <v>99.03308194444445</v>
+      </c>
+      <c r="E798" t="n">
+        <v>1.17456569979046</v>
+      </c>
+      <c r="F798" t="b">
+        <v>1</v>
+      </c>
+      <c r="G798" t="n">
+        <v>0.01728298383277108</v>
+      </c>
+      <c r="H798" t="b">
         <v>1</v>
       </c>
     </row>
